--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_los_lagos.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_los_lagos.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>26.92906407299254</v>
+      </c>
+      <c r="C2">
         <v>22.41816177890898</v>
-      </c>
-      <c r="C2">
-        <v>26.92906407299254</v>
       </c>
       <c r="D2">
         <v>4.46066903193107</v>
       </c>
       <c r="E2">
-        <v>15.01076545013276</v>
+        <v>18.03117796087919</v>
       </c>
       <c r="F2">
-        <v>66.95805658898804</v>
+        <v>66.95805658898806</v>
       </c>
       <c r="G2">
-        <v>18.03117796087919</v>
+        <v>15.01076545013277</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>26.86218302094818</v>
+      </c>
+      <c r="C3">
         <v>32.5909592061742</v>
-      </c>
-      <c r="C3">
-        <v>26.86218302094818</v>
       </c>
       <c r="D3">
         <v>3.068335588633288</v>
       </c>
       <c r="E3">
-        <v>20.43920787697754</v>
+        <v>16.84644319061843</v>
       </c>
       <c r="F3">
         <v>62.71434893240403</v>
       </c>
       <c r="G3">
-        <v>16.84644319061843</v>
+        <v>20.43920787697754</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>24.61538461538462</v>
+      </c>
+      <c r="C4">
         <v>42.22672064777328</v>
-      </c>
-      <c r="C4">
-        <v>24.61538461538462</v>
       </c>
       <c r="D4">
         <v>2.36816874400767</v>
       </c>
       <c r="E4">
-        <v>25.30939092453288</v>
+        <v>14.75370055811696</v>
       </c>
       <c r="F4">
         <v>59.93690851735016</v>
       </c>
       <c r="G4">
-        <v>14.75370055811696</v>
+        <v>25.30939092453288</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>25.64171845447176</v>
+      </c>
+      <c r="C5">
         <v>41.5022966765739</v>
-      </c>
-      <c r="C5">
-        <v>25.64171845447176</v>
       </c>
       <c r="D5">
         <v>2.409505208333333</v>
       </c>
       <c r="E5">
-        <v>24.83026188166828</v>
+        <v>15.34109279017135</v>
       </c>
       <c r="F5">
         <v>59.82864532816036</v>
       </c>
       <c r="G5">
-        <v>15.34109279017135</v>
+        <v>24.83026188166828</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>28.56809701492537</v>
+      </c>
+      <c r="C6">
         <v>30.76803482587065</v>
-      </c>
-      <c r="C6">
-        <v>28.56809701492537</v>
       </c>
       <c r="D6">
         <v>3.250126326427488</v>
       </c>
       <c r="E6">
-        <v>19.31014294774845</v>
+        <v>17.9294530906962</v>
       </c>
       <c r="F6">
         <v>62.76040396155535</v>
       </c>
       <c r="G6">
-        <v>17.9294530906962</v>
+        <v>19.31014294774845</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>27.09859154929578</v>
+      </c>
+      <c r="C7">
         <v>39.30516431924882</v>
-      </c>
-      <c r="C7">
-        <v>27.09859154929578</v>
       </c>
       <c r="D7">
         <v>2.544194935499283</v>
       </c>
       <c r="E7">
-        <v>23.62035887597337</v>
+        <v>16.28484369709965</v>
       </c>
       <c r="F7">
         <v>60.09479742692698</v>
       </c>
       <c r="G7">
-        <v>16.28484369709965</v>
+        <v>23.62035887597337</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>25.67324955116696</v>
+      </c>
+      <c r="C8">
         <v>31.91416602547662</v>
-      </c>
-      <c r="C8">
-        <v>25.67324955116696</v>
       </c>
       <c r="D8">
         <v>3.133404768282882</v>
       </c>
       <c r="E8">
-        <v>20.25172245429393</v>
+        <v>16.29143384147995</v>
       </c>
       <c r="F8">
         <v>63.45684370422611</v>
       </c>
       <c r="G8">
-        <v>16.29143384147995</v>
+        <v>20.25172245429393</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>24.95344506517691</v>
+      </c>
+      <c r="C9">
         <v>42.68813670719685</v>
-      </c>
-      <c r="C9">
-        <v>24.95344506517691</v>
       </c>
       <c r="D9">
         <v>2.342571208622017</v>
       </c>
       <c r="E9">
+        <v>14.88499738630423</v>
+      </c>
+      <c r="F9">
+        <v>59.65107161526399</v>
+      </c>
+      <c r="G9">
         <v>25.46393099843178</v>
-      </c>
-      <c r="F9">
-        <v>59.65107161526398</v>
-      </c>
-      <c r="G9">
-        <v>14.88499738630423</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>28.04226557657684</v>
+      </c>
+      <c r="C10">
         <v>25.4390366281987</v>
-      </c>
-      <c r="C10">
-        <v>28.04226557657684</v>
       </c>
       <c r="D10">
         <v>3.930966469428008</v>
       </c>
       <c r="E10">
-        <v>16.57468125612969</v>
+        <v>18.2708024845676</v>
       </c>
       <c r="F10">
         <v>65.1545162593027</v>
       </c>
       <c r="G10">
-        <v>18.2708024845676</v>
+        <v>16.57468125612969</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>24.237025116386</v>
+      </c>
+      <c r="C11">
         <v>24.88361400080464</v>
-      </c>
-      <c r="C11">
-        <v>24.237025116386</v>
       </c>
       <c r="D11">
         <v>4.018708857835778</v>
       </c>
       <c r="E11">
-        <v>16.68690138945097</v>
+        <v>16.2533001869303</v>
       </c>
       <c r="F11">
         <v>67.05979842361873</v>
       </c>
       <c r="G11">
-        <v>16.2533001869303</v>
+        <v>16.68690138945097</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>24.07380918323559</v>
+      </c>
+      <c r="C12">
         <v>34.33342869403519</v>
-      </c>
-      <c r="C12">
-        <v>24.07380918323559</v>
       </c>
       <c r="D12">
         <v>2.912613269451099</v>
       </c>
       <c r="E12">
-        <v>21.67415400591462</v>
+        <v>15.19741743233176</v>
       </c>
       <c r="F12">
         <v>63.12842856175361</v>
       </c>
       <c r="G12">
-        <v>15.19741743233176</v>
+        <v>21.67415400591462</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>24.72214168357978</v>
+      </c>
+      <c r="C13">
         <v>28.44302696433749</v>
-      </c>
-      <c r="C13">
-        <v>24.72214168357978</v>
       </c>
       <c r="D13">
         <v>3.515800203873598</v>
       </c>
       <c r="E13">
+        <v>16.14083796062595</v>
+      </c>
+      <c r="F13">
+        <v>65.28899545683998</v>
+      </c>
+      <c r="G13">
         <v>18.57016658253407</v>
-      </c>
-      <c r="F13">
-        <v>65.28899545683997</v>
-      </c>
-      <c r="G13">
-        <v>16.14083796062594</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>26.52005174644243</v>
+      </c>
+      <c r="C14">
         <v>37.60241483398016</v>
-      </c>
-      <c r="C14">
-        <v>26.52005174644243</v>
       </c>
       <c r="D14">
         <v>2.65940366972477</v>
       </c>
       <c r="E14">
-        <v>22.91119285338939</v>
+        <v>16.15869679453494</v>
       </c>
       <c r="F14">
         <v>60.93011035207567</v>
       </c>
       <c r="G14">
-        <v>16.15869679453495</v>
+        <v>22.91119285338938</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>25.83803025808366</v>
+      </c>
+      <c r="C15">
         <v>26.63897953129635</v>
-      </c>
-      <c r="C15">
-        <v>25.83803025808366</v>
       </c>
       <c r="D15">
         <v>3.753897550111359</v>
       </c>
       <c r="E15">
+        <v>16.94552529182879</v>
+      </c>
+      <c r="F15">
+        <v>65.58365758754864</v>
+      </c>
+      <c r="G15">
         <v>17.47081712062257</v>
-      </c>
-      <c r="F15">
-        <v>65.58365758754863</v>
-      </c>
-      <c r="G15">
-        <v>16.94552529182879</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>24.34488588334742</v>
+      </c>
+      <c r="C16">
         <v>40.36348267117498</v>
-      </c>
-      <c r="C16">
-        <v>24.34488588334742</v>
       </c>
       <c r="D16">
         <v>2.477486910994764</v>
       </c>
       <c r="E16">
-        <v>24.50603027970234</v>
+        <v>14.78060046189377</v>
       </c>
       <c r="F16">
         <v>60.7133692584039</v>
       </c>
       <c r="G16">
-        <v>14.78060046189377</v>
+        <v>24.50603027970234</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>23.9337822671156</v>
+      </c>
+      <c r="C17">
         <v>32.80022446689113</v>
-      </c>
-      <c r="C17">
-        <v>23.9337822671156</v>
       </c>
       <c r="D17">
         <v>3.048759623609923</v>
       </c>
       <c r="E17">
-        <v>20.92731829573935</v>
+        <v>15.2703186537773</v>
       </c>
       <c r="F17">
         <v>63.80236305048336</v>
       </c>
       <c r="G17">
-        <v>15.2703186537773</v>
+        <v>20.92731829573935</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>27.44005571584917</v>
+      </c>
+      <c r="C18">
         <v>20.0179086658044</v>
-      </c>
-      <c r="C18">
-        <v>27.44005571584917</v>
       </c>
       <c r="D18">
         <v>4.995526838966203</v>
       </c>
       <c r="E18">
-        <v>13.57533229876527</v>
+        <v>18.60873085486809</v>
       </c>
       <c r="F18">
         <v>67.81593684636664</v>
       </c>
       <c r="G18">
-        <v>18.60873085486809</v>
+        <v>13.57533229876527</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>23.71674784563507</v>
+      </c>
+      <c r="C19">
         <v>38.40389659048333</v>
-      </c>
-      <c r="C19">
-        <v>23.71674784563507</v>
       </c>
       <c r="D19">
         <v>2.60390243902439</v>
       </c>
       <c r="E19">
-        <v>23.68846776057315</v>
+        <v>14.6290732609198</v>
       </c>
       <c r="F19">
         <v>61.68245897850705</v>
       </c>
       <c r="G19">
-        <v>14.6290732609198</v>
+        <v>23.68846776057315</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>23.67428003972195</v>
+      </c>
+      <c r="C20">
         <v>37.49751737835154</v>
-      </c>
-      <c r="C20">
-        <v>23.67428003972195</v>
       </c>
       <c r="D20">
         <v>2.666843220338983</v>
       </c>
       <c r="E20">
-        <v>23.26555760936537</v>
+        <v>14.68884781269255</v>
       </c>
       <c r="F20">
         <v>62.04559457794208</v>
       </c>
       <c r="G20">
-        <v>14.68884781269255</v>
+        <v>23.26555760936537</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>25.78372988647694</v>
+      </c>
+      <c r="C21">
         <v>30.9695655753451</v>
-      </c>
-      <c r="C21">
-        <v>25.78372988647694</v>
       </c>
       <c r="D21">
         <v>3.228976517501108</v>
       </c>
       <c r="E21">
-        <v>19.75688325027136</v>
+        <v>16.44860467559145</v>
       </c>
       <c r="F21">
         <v>63.79451207413719</v>
       </c>
       <c r="G21">
-        <v>16.44860467559145</v>
+        <v>19.75688325027136</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>27.12242244101802</v>
+      </c>
+      <c r="C22">
         <v>36.169422255248</v>
-      </c>
-      <c r="C22">
-        <v>27.12242244101802</v>
       </c>
       <c r="D22">
         <v>2.764766307139189</v>
       </c>
       <c r="E22">
-        <v>22.15017064846416</v>
+        <v>16.60978384527872</v>
       </c>
       <c r="F22">
         <v>61.24004550625711</v>
       </c>
       <c r="G22">
-        <v>16.60978384527872</v>
+        <v>22.15017064846416</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>26.41647077895761</v>
+      </c>
+      <c r="C23">
         <v>40.30153197697982</v>
-      </c>
-      <c r="C23">
-        <v>26.41647077895761</v>
       </c>
       <c r="D23">
         <v>2.481295253419147</v>
       </c>
       <c r="E23">
-        <v>24.17347335667056</v>
+        <v>15.84500194476857</v>
       </c>
       <c r="F23">
         <v>59.98152469856088</v>
       </c>
       <c r="G23">
-        <v>15.84500194476857</v>
+        <v>24.17347335667056</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>25.44606093878671</v>
+      </c>
+      <c r="C24">
         <v>38.18281636014274</v>
-      </c>
-      <c r="C24">
-        <v>25.44606093878671</v>
       </c>
       <c r="D24">
         <v>2.618979151689432</v>
       </c>
       <c r="E24">
-        <v>23.33501090421071</v>
+        <v>15.5510820332159</v>
       </c>
       <c r="F24">
-        <v>61.1139070625734</v>
+        <v>61.11390706257339</v>
       </c>
       <c r="G24">
-        <v>15.5510820332159</v>
+        <v>23.3350109042107</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>26.91614066726781</v>
+      </c>
+      <c r="C25">
         <v>41.309738503156</v>
-      </c>
-      <c r="C25">
-        <v>26.91614066726781</v>
       </c>
       <c r="D25">
         <v>2.420736698499318</v>
       </c>
       <c r="E25">
+        <v>16</v>
+      </c>
+      <c r="F25">
+        <v>59.44388609715243</v>
+      </c>
+      <c r="G25">
         <v>24.55611390284757</v>
-      </c>
-      <c r="F25">
-        <v>59.44388609715244</v>
-      </c>
-      <c r="G25">
-        <v>16</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>23.58963643961555</v>
+      </c>
+      <c r="C26">
         <v>45.98829920601755</v>
-      </c>
-      <c r="C26">
-        <v>23.58963643961555</v>
       </c>
       <c r="D26">
         <v>2.174466151749205</v>
       </c>
       <c r="E26">
-        <v>27.11927057663874</v>
+        <v>13.91079349433218</v>
       </c>
       <c r="F26">
         <v>58.96993592902908</v>
       </c>
       <c r="G26">
-        <v>13.91079349433218</v>
+        <v>27.11927057663874</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>26.11009732360097</v>
+      </c>
+      <c r="C27">
         <v>43.56751824817518</v>
-      </c>
-      <c r="C27">
-        <v>26.11009732360097</v>
       </c>
       <c r="D27">
         <v>2.295287958115183</v>
       </c>
       <c r="E27">
-        <v>25.67664455995698</v>
+        <v>15.38806237677003</v>
       </c>
       <c r="F27">
         <v>58.93529306327299</v>
       </c>
       <c r="G27">
-        <v>15.38806237677003</v>
+        <v>25.67664455995698</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>24.36829352717203</v>
+      </c>
+      <c r="C28">
         <v>32.64105226722049</v>
-      </c>
-      <c r="C28">
-        <v>24.36829352717203</v>
       </c>
       <c r="D28">
         <v>3.063626723223754</v>
       </c>
       <c r="E28">
-        <v>20.78924162257496</v>
+        <v>15.52028218694885</v>
       </c>
       <c r="F28">
         <v>63.6904761904762</v>
       </c>
       <c r="G28">
-        <v>15.52028218694885</v>
+        <v>20.78924162257496</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>33.00492610837438</v>
+      </c>
+      <c r="C29">
         <v>33.43596059113301</v>
-      </c>
-      <c r="C29">
-        <v>33.00492610837438</v>
       </c>
       <c r="D29">
         <v>2.990791896869245</v>
       </c>
       <c r="E29">
-        <v>20.08879023307437</v>
+        <v>19.82981871994081</v>
       </c>
       <c r="F29">
         <v>60.08139104698483</v>
       </c>
       <c r="G29">
-        <v>19.82981871994081</v>
+        <v>20.08879023307437</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>26.51231045165498</v>
+      </c>
+      <c r="C30">
         <v>28.42002282732757</v>
-      </c>
-      <c r="C30">
-        <v>26.51231045165498</v>
       </c>
       <c r="D30">
         <v>3.518646012621916</v>
       </c>
       <c r="E30">
-        <v>18.34350663018312</v>
+        <v>17.11218690801936</v>
       </c>
       <c r="F30">
         <v>64.54430646179752</v>
       </c>
       <c r="G30">
-        <v>17.11218690801936</v>
+        <v>18.34350663018312</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>25.84</v>
+      </c>
+      <c r="C31">
         <v>36.16</v>
-      </c>
-      <c r="C31">
-        <v>25.84</v>
       </c>
       <c r="D31">
         <v>2.765486725663717</v>
       </c>
       <c r="E31">
-        <v>22.32098765432098</v>
+        <v>15.95061728395062</v>
       </c>
       <c r="F31">
         <v>61.72839506172839</v>
       </c>
       <c r="G31">
-        <v>15.95061728395062</v>
+        <v>22.32098765432098</v>
       </c>
     </row>
   </sheetData>
